--- a/data/trans_orig/Q23_tabaco-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media de inicio en el consumo de tabaco</t>
+          <t>Edad media de inicio en el consumo de tabaco (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 16,24</t>
+          <t>15,77; 16,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,59</t>
+          <t>15,92; 16,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,88</t>
+          <t>16,02; 16,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 16,56</t>
+          <t>15,93; 16,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,48</t>
+          <t>16,67; 17,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 18,35</t>
+          <t>17,21; 18,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 18,76</t>
+          <t>17,36; 18,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,8</t>
+          <t>16,95; 17,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 16,56</t>
+          <t>16,14; 16,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,42; 17,0</t>
+          <t>16,43; 17,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,39</t>
+          <t>16,62; 17,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,38; 16,89</t>
+          <t>16,38; 16,88</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 17,08</t>
+          <t>16,34; 17,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,9</t>
+          <t>16,35; 16,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 17,02</t>
+          <t>16,22; 16,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,03; 16,7</t>
+          <t>16,05; 16,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 18,06</t>
+          <t>17,17; 18,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,17</t>
+          <t>17,26; 18,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 17,82</t>
+          <t>16,93; 17,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,47</t>
+          <t>16,87; 17,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 17,3</t>
+          <t>16,68; 17,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 17,3</t>
+          <t>16,76; 17,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,17</t>
+          <t>16,63; 17,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,87</t>
+          <t>16,24; 16,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,01; 16,59</t>
+          <t>15,98; 16,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 16,89</t>
+          <t>16,2; 16,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,82</t>
+          <t>16,19; 16,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,75; 17,76</t>
+          <t>16,76; 17,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,4; 19,12</t>
+          <t>17,41; 19,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,99</t>
+          <t>16,92; 17,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 18,28</t>
+          <t>17,22; 18,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 18,26</t>
+          <t>17,32; 18,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,36</t>
+          <t>16,61; 17,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,22</t>
+          <t>16,62; 17,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,69; 17,3</t>
+          <t>16,69; 17,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,76</t>
+          <t>17,06; 17,77</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,17; 16,67</t>
+          <t>16,15; 16,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,83</t>
+          <t>16,3; 16,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,95</t>
+          <t>16,21; 16,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 17,02</t>
+          <t>16,4; 17,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 18,02</t>
+          <t>16,99; 17,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 18,79</t>
+          <t>17,46; 18,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 18,36</t>
+          <t>17,38; 18,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 18,1</t>
+          <t>17,27; 18,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,14</t>
+          <t>16,6; 17,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,43</t>
+          <t>16,87; 17,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,4</t>
+          <t>16,85; 17,34</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,53</t>
+          <t>16,22; 16,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 16,66</t>
+          <t>16,34; 16,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,7</t>
+          <t>16,32; 16,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,76</t>
+          <t>16,31; 16,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,81</t>
+          <t>17,22; 17,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,99</t>
+          <t>17,42; 18,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,97</t>
+          <t>17,42; 17,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,69</t>
+          <t>17,27; 17,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,94</t>
+          <t>16,65; 16,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,12</t>
+          <t>16,83; 17,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,14</t>
+          <t>16,84; 17,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,05</t>
+          <t>16,63; 17,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,22</t>
+          <t>16,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,31</t>
+          <t>17,29</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,62</t>
+          <t>16,67</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,77; 16,24</t>
+          <t>15,79; 16,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 16,56</t>
+          <t>15,93; 16,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,8</t>
+          <t>15,98; 16,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,56</t>
+          <t>16,01; 16,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,46</t>
+          <t>16,66; 17,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 18,29</t>
+          <t>17,17; 18,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 18,78</t>
+          <t>17,28; 18,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,95; 17,74</t>
+          <t>16,97; 17,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 16,56</t>
+          <t>16,14; 16,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,04</t>
+          <t>16,42; 17,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,62; 17,33</t>
+          <t>16,6; 17,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,38; 16,88</t>
+          <t>16,43; 16,94</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,34</t>
+          <t>16,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,57</t>
+          <t>16,79</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,04</t>
+          <t>16,32; 17,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,35; 16,92</t>
+          <t>16,35; 16,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,95</t>
+          <t>16,25; 16,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,05; 16,73</t>
+          <t>16,26; 16,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 18,06</t>
+          <t>17,1; 18,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 18,16</t>
+          <t>17,26; 18,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,78</t>
+          <t>16,95; 17,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,5</t>
+          <t>16,87; 17,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,28</t>
+          <t>16,7; 17,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,28</t>
+          <t>16,77; 17,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,17</t>
+          <t>16,61; 17,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 16,85</t>
+          <t>16,59; 17,02</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,18</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,73</t>
+          <t>17,96</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>17,54</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 16,61</t>
+          <t>16,0; 16,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 16,93</t>
+          <t>16,22; 16,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,81</t>
+          <t>16,18; 16,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,69</t>
+          <t>16,83; 17,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 19,17</t>
+          <t>17,39; 19,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,92; 17,97</t>
+          <t>16,87; 18,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,22; 18,33</t>
+          <t>17,18; 18,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 18,32</t>
+          <t>17,48; 18,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,31</t>
+          <t>16,61; 17,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 17,21</t>
+          <t>16,59; 17,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,69; 17,27</t>
+          <t>16,73; 17,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,77</t>
+          <t>17,21; 17,94</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,68</t>
+          <t>16,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,61</t>
+          <t>17,66</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,09</t>
+          <t>17,1</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,68</t>
+          <t>16,17; 16,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,84</t>
+          <t>16,32; 16,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 16,94</t>
+          <t>16,22; 16,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 17,03</t>
+          <t>16,36; 16,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,99</t>
+          <t>17,0; 17,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 18,74</t>
+          <t>17,41; 18,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 18,35</t>
+          <t>17,4; 18,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,06</t>
+          <t>17,27; 18,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,53</t>
+          <t>16,93; 17,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,46</t>
+          <t>16,84; 17,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 17,34</t>
+          <t>16,86; 17,33</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,57</t>
+          <t>16,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>17,53</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>17,04</t>
         </is>
       </c>
     </row>
@@ -1281,57 +1281,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,66</t>
+          <t>16,36; 16,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,68</t>
+          <t>16,31; 16,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,78</t>
+          <t>16,54; 16,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,8</t>
+          <t>17,26; 17,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,0</t>
+          <t>17,42; 17,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,42; 17,94</t>
+          <t>17,43; 17,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,27; 17,7</t>
+          <t>17,33; 17,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,93</t>
+          <t>16,66; 16,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,11</t>
+          <t>16,84; 17,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,14</t>
+          <t>16,82; 17,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,06</t>
+          <t>16,93; 17,18</t>
         </is>
       </c>
     </row>
